--- a/docs/Estimacion.xlsx
+++ b/docs/Estimacion.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\Desarrollos\paysandu-gestion-baby\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CEE5165-634F-4F22-AE6E-DAE427EE471E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4FA155-298C-4FE2-B1D5-7A6B891403B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{2A1F74DB-281B-42A6-B1CB-9D45707DD6B3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A1F74DB-281B-42A6-B1CB-9D45707DD6B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>$/usd</t>
   </si>
@@ -292,15 +291,37 @@
   </si>
   <si>
     <t>Venta de app</t>
+  </si>
+  <si>
+    <t>E. Colorado</t>
+  </si>
+  <si>
+    <t>E. Blanco</t>
+  </si>
+  <si>
+    <t>Totales</t>
+  </si>
+  <si>
+    <t>Leña</t>
+  </si>
+  <si>
+    <t>Kg</t>
+  </si>
+  <si>
+    <t>Algarrobo (asado)</t>
+  </si>
+  <si>
+    <t>Leña de monte (asado)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -387,14 +408,14 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -413,9 +434,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -431,13 +449,15 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -776,12 +796,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D86C825-9CA9-4D12-B264-5DD8DFE82DE7}">
   <dimension ref="B1:T36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +810,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="2:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B4" s="14" t="s">
         <v>54</v>
       </c>
@@ -820,17 +841,17 @@
       <c r="K4" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="O4" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>1</v>
       </c>
@@ -877,11 +898,11 @@
         <v>31500</v>
       </c>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="16">
         <v>8000</v>
       </c>
       <c r="D6" s="10">
@@ -924,11 +945,11 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B7" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="16">
         <v>8000</v>
       </c>
       <c r="D7" s="10">
@@ -974,17 +995,17 @@
         <v>24000</v>
       </c>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B8" s="8"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="N8" s="16" t="s">
+      <c r="N8" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="16">
         <f>+SUM(O5:O7)</f>
         <v>35500</v>
       </c>
@@ -992,7 +1013,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B9" s="8"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -1004,7 +1025,7 @@
         <v>16.96113074204947</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B10" s="8"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -1012,38 +1033,38 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="R12" s="21">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="R12">
         <v>700</v>
       </c>
       <c r="S12" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
       <c r="F13">
         <v>2026</v>
       </c>
-      <c r="R13" s="22">
+      <c r="R13" s="3">
         <v>0.2</v>
       </c>
       <c r="S13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="F14">
         <v>6</v>
       </c>
       <c r="G14">
-        <f>+$F$13-F14</f>
+        <f t="shared" ref="G14:G20" si="0">+$F$13-F14</f>
         <v>2020</v>
       </c>
       <c r="H14">
@@ -1052,7 +1073,7 @@
       <c r="I14">
         <v>45</v>
       </c>
-      <c r="R14" s="21">
+      <c r="R14">
         <f>+R13*R12</f>
         <v>140</v>
       </c>
@@ -1060,12 +1081,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
       <c r="F15">
         <v>7</v>
       </c>
       <c r="G15">
-        <f>+$F$13-F15</f>
+        <f t="shared" si="0"/>
         <v>2019</v>
       </c>
       <c r="H15">
@@ -1080,19 +1101,19 @@
       <c r="O15" t="s">
         <v>68</v>
       </c>
-      <c r="R15" s="21">
+      <c r="R15">
         <v>100</v>
       </c>
       <c r="S15" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="F16">
         <v>8</v>
       </c>
       <c r="G16">
-        <f>+$F$13-F16</f>
+        <f t="shared" si="0"/>
         <v>2018</v>
       </c>
       <c r="H16">
@@ -1104,7 +1125,7 @@
       <c r="O16">
         <v>24</v>
       </c>
-      <c r="R16" s="21">
+      <c r="R16">
         <f>+R15*R14</f>
         <v>14000</v>
       </c>
@@ -1112,12 +1133,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="6:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:20" x14ac:dyDescent="0.3">
       <c r="F17">
         <v>9</v>
       </c>
       <c r="G17">
-        <f>+$F$13-F17</f>
+        <f t="shared" si="0"/>
         <v>2017</v>
       </c>
       <c r="H17">
@@ -1132,22 +1153,22 @@
       <c r="O17">
         <v>1674</v>
       </c>
-      <c r="R17" s="21">
+      <c r="R17">
         <v>40</v>
       </c>
       <c r="S17" t="s">
         <v>75</v>
       </c>
-      <c r="T17" s="24" t="s">
+      <c r="T17" s="20" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="6:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.3">
       <c r="F18">
         <v>10</v>
       </c>
       <c r="G18">
-        <f>+$F$13-F18</f>
+        <f t="shared" si="0"/>
         <v>2016</v>
       </c>
       <c r="H18">
@@ -1164,20 +1185,20 @@
         <f>+O17*O16</f>
         <v>40176</v>
       </c>
-      <c r="R18" s="21">
+      <c r="R18">
         <v>39</v>
       </c>
       <c r="S18" t="s">
         <v>76</v>
       </c>
-      <c r="T18" s="24"/>
-    </row>
-    <row r="19" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="T18" s="20"/>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.3">
       <c r="F19">
         <v>11</v>
       </c>
       <c r="G19">
-        <f>+$F$13-F19</f>
+        <f t="shared" si="0"/>
         <v>2015</v>
       </c>
       <c r="H19">
@@ -1187,21 +1208,21 @@
         <f>+K18-K17</f>
         <v>9</v>
       </c>
-      <c r="R19" s="21">
+      <c r="R19">
         <f>+R16*R17/R18</f>
         <v>14358.974358974359</v>
       </c>
       <c r="S19" t="s">
         <v>77</v>
       </c>
-      <c r="T19" s="24"/>
-    </row>
-    <row r="20" spans="6:20" x14ac:dyDescent="0.25">
+      <c r="T19" s="20"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.3">
       <c r="F20">
         <v>12</v>
       </c>
       <c r="G20">
-        <f>+$F$13-F20</f>
+        <f t="shared" si="0"/>
         <v>2014</v>
       </c>
       <c r="H20">
@@ -1215,14 +1236,14 @@
         <f>3337+1113</f>
         <v>4450</v>
       </c>
-      <c r="R20" s="21">
+      <c r="R20">
         <v>600</v>
       </c>
       <c r="S20" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="6:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.3">
       <c r="F21">
         <v>13</v>
       </c>
@@ -1236,15 +1257,15 @@
         <f>+L20*K20</f>
         <v>20025</v>
       </c>
-      <c r="R21" s="21">
+      <c r="R21">
         <v>11</v>
       </c>
       <c r="S21" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="6:20" x14ac:dyDescent="0.25">
-      <c r="R22" s="21">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="R22">
         <f>+R21*R20</f>
         <v>6600</v>
       </c>
@@ -1252,8 +1273,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="6:20" x14ac:dyDescent="0.25">
-      <c r="R23" s="21">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="R23">
         <f>+R22*R16</f>
         <v>92400000</v>
       </c>
@@ -1261,8 +1282,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="6:20" x14ac:dyDescent="0.25">
-      <c r="R24" s="23">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C24" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="R24" s="1">
         <f>+R23/R18</f>
         <v>2369230.769230769</v>
       </c>
@@ -1270,7 +1297,20 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="6:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C25" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="18">
+        <v>1250</v>
+      </c>
+      <c r="E25" s="18">
+        <v>7</v>
+      </c>
+      <c r="F25" s="18">
+        <f>+E25*D25</f>
+        <v>8750</v>
+      </c>
       <c r="R25" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -1278,7 +1318,20 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="6:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C26" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="18">
+        <v>1250</v>
+      </c>
+      <c r="E26" s="18">
+        <v>8</v>
+      </c>
+      <c r="F26" s="18">
+        <f>+E26*D26</f>
+        <v>10000</v>
+      </c>
       <c r="R26">
         <f>+R24*R25</f>
         <v>11846.153846153846</v>
@@ -1287,33 +1340,80 @@
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="6:20" x14ac:dyDescent="0.25">
-      <c r="N31" s="18" t="s">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C27" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="18">
+        <v>200</v>
+      </c>
+      <c r="E27" s="18">
+        <v>9</v>
+      </c>
+      <c r="F27" s="18">
+        <f>+E27*D27</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C28" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="18">
+        <v>200</v>
+      </c>
+      <c r="E28" s="18">
+        <v>6.5</v>
+      </c>
+      <c r="F28" s="18">
+        <f>+E28*D28</f>
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="C29" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="18">
+        <f>+SUM(D25:D28)</f>
+        <v>2900</v>
+      </c>
+      <c r="E29" s="22">
+        <f>+F29/D29</f>
+        <v>7.5344827586206895</v>
+      </c>
+      <c r="F29" s="18">
+        <f>+SUM(F25:F28)</f>
+        <v>21850</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.3">
+      <c r="N31" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="O31" s="18" t="s">
+      <c r="O31" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="P31" s="18" t="s">
+      <c r="P31" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="Q31" s="18" t="s">
+      <c r="Q31" s="17" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="6:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:20" x14ac:dyDescent="0.3">
       <c r="J32">
         <f>143*40</f>
         <v>5720</v>
       </c>
-      <c r="N32" s="19">
+      <c r="N32" s="18">
         <v>4374</v>
       </c>
-      <c r="O32" s="18"/>
-      <c r="P32" s="19">
+      <c r="O32" s="17"/>
+      <c r="P32" s="18">
         <v>1969</v>
       </c>
-      <c r="Q32" s="19">
+      <c r="Q32" s="18">
         <f>+P32+N32</f>
         <v>6343</v>
       </c>
@@ -1322,7 +1422,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="33" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:19" x14ac:dyDescent="0.3">
       <c r="J33">
         <v>6490</v>
       </c>
@@ -1330,18 +1430,18 @@
         <f>+J33*0.75</f>
         <v>4867.5</v>
       </c>
-      <c r="N33" s="19">
+      <c r="N33" s="18">
         <v>3144</v>
       </c>
-      <c r="O33" s="20">
+      <c r="O33" s="19">
         <f>+N33/$N$32</f>
         <v>0.71879286694101507</v>
       </c>
-      <c r="P33" s="19">
+      <c r="P33" s="18">
         <f>+O33*$S$32</f>
         <v>1415.3031550068588</v>
       </c>
-      <c r="Q33" s="19">
+      <c r="Q33" s="18">
         <f>+P33+N33</f>
         <v>4559.303155006859</v>
       </c>
@@ -1349,19 +1449,19 @@
         <v>254</v>
       </c>
     </row>
-    <row r="34" spans="10:19" x14ac:dyDescent="0.25">
-      <c r="N34" s="19">
+    <row r="34" spans="10:19" x14ac:dyDescent="0.3">
+      <c r="N34" s="18">
         <v>635</v>
       </c>
-      <c r="O34" s="20">
+      <c r="O34" s="19">
         <f>+N34/$N$32</f>
         <v>0.14517604023776864</v>
       </c>
-      <c r="P34" s="19">
+      <c r="P34" s="18">
         <f>+O34*$S$32</f>
         <v>285.85162322816649</v>
       </c>
-      <c r="Q34" s="19">
+      <c r="Q34" s="18">
         <f>+P34+N34</f>
         <v>920.85162322816655</v>
       </c>
@@ -1369,19 +1469,19 @@
         <v>306</v>
       </c>
     </row>
-    <row r="35" spans="10:19" x14ac:dyDescent="0.25">
-      <c r="N35" s="19">
+    <row r="35" spans="10:19" x14ac:dyDescent="0.3">
+      <c r="N35" s="18">
         <v>593</v>
       </c>
-      <c r="O35" s="20">
+      <c r="O35" s="19">
         <f>+N35/$N$32</f>
         <v>0.13557384545038867</v>
       </c>
-      <c r="P35" s="19">
+      <c r="P35" s="18">
         <f>+O35*$S$32</f>
         <v>266.94490169181529</v>
       </c>
-      <c r="Q35" s="19">
+      <c r="Q35" s="18">
         <f>+P35+N35</f>
         <v>859.94490169181529</v>
       </c>
@@ -1389,7 +1489,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="36" spans="10:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="10:19" x14ac:dyDescent="0.3">
       <c r="S36">
         <v>1156</v>
       </c>
@@ -1405,14 +1505,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2717175-3BED-450E-BA44-36B91576D66D}">
   <dimension ref="A1:Q35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F1" t="s">
         <v>0</v>
       </c>
@@ -1420,7 +1520,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F3">
         <f>260*3</f>
         <v>780</v>
@@ -1429,17 +1529,17 @@
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="J4">
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="J5">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>1</v>
       </c>
@@ -1447,7 +1547,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>2</v>
       </c>
@@ -1473,7 +1573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>60000</v>
       </c>
@@ -1510,7 +1610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="M9" t="s">
         <v>11</v>
       </c>
@@ -1522,7 +1622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>13</v>
       </c>
@@ -1530,12 +1630,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="Q11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="M12" t="s">
         <v>16</v>
       </c>
@@ -1546,7 +1646,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="M13" t="s">
         <v>18</v>
       </c>
@@ -1558,7 +1658,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>20</v>
       </c>
@@ -1577,7 +1677,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>2</v>
       </c>
@@ -1610,7 +1710,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>6000</v>
       </c>
@@ -1640,7 +1740,7 @@
         <v>84642.857142857145</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -1662,7 +1762,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -1684,7 +1784,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -1703,7 +1803,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -1722,7 +1822,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="N22" t="s">
         <v>32</v>
       </c>
@@ -1730,7 +1830,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2" t="s">
@@ -1752,7 +1852,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2" t="s">
@@ -1774,7 +1874,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2" t="s">
@@ -1797,7 +1897,7 @@
       </c>
       <c r="Q25" s="6"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>37</v>
       </c>
@@ -1811,7 +1911,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>39</v>
       </c>
@@ -1829,7 +1929,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>42</v>
       </c>
@@ -1847,7 +1947,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>45</v>
       </c>
@@ -1862,17 +1962,17 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>50</v>
       </c>
@@ -1909,7 +2009,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" ht="16.8" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
         <v>52</v>
       </c>
@@ -1924,7 +2024,7 @@
         <v>47000</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="I34">
         <v>2.5910299999999998E-3</v>
       </c>
@@ -1932,7 +2032,7 @@
         <v>47000</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="I35">
         <f>+I34+I32</f>
         <v>3.2696910000000003E-2</v>
